--- a/Opptaksområder/KLASS TSB/OPPTAK_TSB_2020.xlsx
+++ b/Opptaksområder/KLASS TSB/OPPTAK_TSB_2020.xlsx
@@ -899,6 +899,9 @@
     <t xml:space="preserve">4618</t>
   </si>
   <si>
+    <t xml:space="preserve">4619</t>
+  </si>
+  <si>
     <t xml:space="preserve">4620</t>
   </si>
   <si>
@@ -1242,9 +1245,6 @@
   </si>
   <si>
     <t xml:space="preserve">5444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4619</t>
   </si>
 </sst>
 </file>
@@ -5845,10 +5845,10 @@
         <v>295</v>
       </c>
       <c r="B252" t="s">
-        <v>282</v>
+        <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>283</v>
+        <v>24</v>
       </c>
       <c r="D252" t="s">
         <v>19</v>
@@ -6117,10 +6117,10 @@
         <v>311</v>
       </c>
       <c r="B268" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C268" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D268" t="s">
         <v>19</v>
@@ -6389,27 +6389,27 @@
         <v>327</v>
       </c>
       <c r="B284" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="C284" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="D284" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E284" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
+        <v>328</v>
+      </c>
+      <c r="B285" t="s">
+        <v>329</v>
+      </c>
+      <c r="C285" t="s">
         <v>330</v>
-      </c>
-      <c r="B285" t="s">
-        <v>331</v>
-      </c>
-      <c r="C285" t="s">
-        <v>332</v>
       </c>
       <c r="D285" t="s">
         <v>48</v>
@@ -6420,13 +6420,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
+        <v>331</v>
+      </c>
+      <c r="B286" t="s">
+        <v>332</v>
+      </c>
+      <c r="C286" t="s">
         <v>333</v>
-      </c>
-      <c r="B286" t="s">
-        <v>331</v>
-      </c>
-      <c r="C286" t="s">
-        <v>332</v>
       </c>
       <c r="D286" t="s">
         <v>48</v>
@@ -6440,10 +6440,10 @@
         <v>334</v>
       </c>
       <c r="B287" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C287" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D287" t="s">
         <v>48</v>
@@ -6457,10 +6457,10 @@
         <v>335</v>
       </c>
       <c r="B288" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C288" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D288" t="s">
         <v>48</v>
@@ -6474,10 +6474,10 @@
         <v>336</v>
       </c>
       <c r="B289" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C289" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D289" t="s">
         <v>48</v>
@@ -6491,10 +6491,10 @@
         <v>337</v>
       </c>
       <c r="B290" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C290" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D290" t="s">
         <v>48</v>
@@ -6508,10 +6508,10 @@
         <v>338</v>
       </c>
       <c r="B291" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C291" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D291" t="s">
         <v>48</v>
@@ -6525,10 +6525,10 @@
         <v>339</v>
       </c>
       <c r="B292" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C292" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D292" t="s">
         <v>48</v>
@@ -6542,10 +6542,10 @@
         <v>340</v>
       </c>
       <c r="B293" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C293" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D293" t="s">
         <v>48</v>
@@ -6559,10 +6559,10 @@
         <v>341</v>
       </c>
       <c r="B294" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C294" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D294" t="s">
         <v>48</v>
@@ -6576,10 +6576,10 @@
         <v>342</v>
       </c>
       <c r="B295" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C295" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D295" t="s">
         <v>48</v>
@@ -6593,10 +6593,10 @@
         <v>343</v>
       </c>
       <c r="B296" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C296" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D296" t="s">
         <v>48</v>
@@ -6610,10 +6610,10 @@
         <v>344</v>
       </c>
       <c r="B297" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C297" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D297" t="s">
         <v>48</v>
@@ -6627,10 +6627,10 @@
         <v>345</v>
       </c>
       <c r="B298" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C298" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D298" t="s">
         <v>48</v>
@@ -6644,10 +6644,10 @@
         <v>346</v>
       </c>
       <c r="B299" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C299" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D299" t="s">
         <v>48</v>
@@ -6661,10 +6661,10 @@
         <v>347</v>
       </c>
       <c r="B300" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C300" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D300" t="s">
         <v>48</v>
@@ -6678,10 +6678,10 @@
         <v>348</v>
       </c>
       <c r="B301" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C301" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D301" t="s">
         <v>48</v>
@@ -6695,10 +6695,10 @@
         <v>349</v>
       </c>
       <c r="B302" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C302" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D302" t="s">
         <v>48</v>
@@ -6712,10 +6712,10 @@
         <v>350</v>
       </c>
       <c r="B303" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C303" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D303" t="s">
         <v>48</v>
@@ -6729,10 +6729,10 @@
         <v>351</v>
       </c>
       <c r="B304" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C304" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D304" t="s">
         <v>48</v>
@@ -6746,10 +6746,10 @@
         <v>352</v>
       </c>
       <c r="B305" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C305" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D305" t="s">
         <v>48</v>
@@ -6763,10 +6763,10 @@
         <v>353</v>
       </c>
       <c r="B306" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C306" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D306" t="s">
         <v>48</v>
@@ -6780,10 +6780,10 @@
         <v>354</v>
       </c>
       <c r="B307" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C307" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D307" t="s">
         <v>48</v>
@@ -6797,10 +6797,10 @@
         <v>355</v>
       </c>
       <c r="B308" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C308" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D308" t="s">
         <v>48</v>
@@ -6814,10 +6814,10 @@
         <v>356</v>
       </c>
       <c r="B309" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D309" t="s">
         <v>48</v>
@@ -6831,10 +6831,10 @@
         <v>357</v>
       </c>
       <c r="B310" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C310" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D310" t="s">
         <v>48</v>
@@ -6848,10 +6848,10 @@
         <v>358</v>
       </c>
       <c r="B311" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C311" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D311" t="s">
         <v>48</v>
@@ -6865,10 +6865,10 @@
         <v>359</v>
       </c>
       <c r="B312" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C312" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D312" t="s">
         <v>48</v>
@@ -6882,10 +6882,10 @@
         <v>360</v>
       </c>
       <c r="B313" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C313" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D313" t="s">
         <v>48</v>
@@ -6899,10 +6899,10 @@
         <v>361</v>
       </c>
       <c r="B314" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C314" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D314" t="s">
         <v>48</v>
@@ -6916,10 +6916,10 @@
         <v>362</v>
       </c>
       <c r="B315" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C315" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D315" t="s">
         <v>48</v>
@@ -6933,10 +6933,10 @@
         <v>363</v>
       </c>
       <c r="B316" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C316" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D316" t="s">
         <v>48</v>
@@ -6950,10 +6950,10 @@
         <v>364</v>
       </c>
       <c r="B317" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C317" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D317" t="s">
         <v>48</v>
@@ -6967,10 +6967,10 @@
         <v>365</v>
       </c>
       <c r="B318" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C318" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D318" t="s">
         <v>48</v>
@@ -6984,10 +6984,10 @@
         <v>366</v>
       </c>
       <c r="B319" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C319" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D319" t="s">
         <v>48</v>
@@ -7001,10 +7001,10 @@
         <v>367</v>
       </c>
       <c r="B320" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C320" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D320" t="s">
         <v>48</v>
@@ -7018,10 +7018,10 @@
         <v>368</v>
       </c>
       <c r="B321" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C321" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D321" t="s">
         <v>48</v>
@@ -7035,16 +7035,16 @@
         <v>369</v>
       </c>
       <c r="B322" t="s">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="C322" t="s">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="D322" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="E322" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="323">
@@ -7069,10 +7069,10 @@
         <v>371</v>
       </c>
       <c r="B324" t="s">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="C324" t="s">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="D324" t="s">
         <v>78</v>
@@ -7083,13 +7083,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
+        <v>372</v>
+      </c>
+      <c r="B325" t="s">
+        <v>373</v>
+      </c>
+      <c r="C325" t="s">
         <v>374</v>
-      </c>
-      <c r="B325" t="s">
-        <v>372</v>
-      </c>
-      <c r="C325" t="s">
-        <v>373</v>
       </c>
       <c r="D325" t="s">
         <v>78</v>
@@ -7103,10 +7103,10 @@
         <v>375</v>
       </c>
       <c r="B326" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C326" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D326" t="s">
         <v>78</v>
@@ -7120,10 +7120,10 @@
         <v>376</v>
       </c>
       <c r="B327" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C327" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D327" t="s">
         <v>78</v>
@@ -7137,10 +7137,10 @@
         <v>377</v>
       </c>
       <c r="B328" t="s">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="C328" t="s">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="D328" t="s">
         <v>78</v>
@@ -7460,10 +7460,10 @@
         <v>396</v>
       </c>
       <c r="B347" t="s">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="C347" t="s">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="D347" t="s">
         <v>78</v>
@@ -7477,10 +7477,10 @@
         <v>397</v>
       </c>
       <c r="B348" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C348" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D348" t="s">
         <v>78</v>
@@ -7494,10 +7494,10 @@
         <v>398</v>
       </c>
       <c r="B349" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C349" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D349" t="s">
         <v>78</v>
@@ -7511,10 +7511,10 @@
         <v>399</v>
       </c>
       <c r="B350" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D350" t="s">
         <v>78</v>
@@ -7528,10 +7528,10 @@
         <v>400</v>
       </c>
       <c r="B351" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C351" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D351" t="s">
         <v>78</v>
@@ -7545,10 +7545,10 @@
         <v>401</v>
       </c>
       <c r="B352" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C352" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D352" t="s">
         <v>78</v>
@@ -7562,10 +7562,10 @@
         <v>402</v>
       </c>
       <c r="B353" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C353" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D353" t="s">
         <v>78</v>
@@ -7579,10 +7579,10 @@
         <v>403</v>
       </c>
       <c r="B354" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C354" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D354" t="s">
         <v>78</v>
@@ -7596,10 +7596,10 @@
         <v>404</v>
       </c>
       <c r="B355" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C355" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D355" t="s">
         <v>78</v>
@@ -7613,10 +7613,10 @@
         <v>405</v>
       </c>
       <c r="B356" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C356" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D356" t="s">
         <v>78</v>
@@ -7630,10 +7630,10 @@
         <v>406</v>
       </c>
       <c r="B357" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C357" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D357" t="s">
         <v>78</v>
@@ -7647,10 +7647,10 @@
         <v>407</v>
       </c>
       <c r="B358" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C358" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D358" t="s">
         <v>78</v>
@@ -7664,10 +7664,10 @@
         <v>408</v>
       </c>
       <c r="B359" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C359" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D359" t="s">
         <v>78</v>
@@ -7681,10 +7681,10 @@
         <v>409</v>
       </c>
       <c r="B360" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C360" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D360" t="s">
         <v>78</v>
@@ -7698,16 +7698,16 @@
         <v>410</v>
       </c>
       <c r="B361" t="s">
-        <v>282</v>
+        <v>373</v>
       </c>
       <c r="C361" t="s">
-        <v>283</v>
+        <v>374</v>
       </c>
       <c r="D361" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="E361" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
